--- a/compare/cxt_with_disagreements.xlsx
+++ b/compare/cxt_with_disagreements.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="cxt evaluation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="修改理由" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,8 +26,11 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
         <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +62,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -755,9 +767,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -981,9 +993,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1061,9 +1073,9 @@
           <t>Single-turn</t>
         </is>
       </c>
-      <c r="AD3" s="1" t="inlineStr">
-        <is>
-          <t>Full Disclosure</t>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1260,9 +1272,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1458,7 +1470,7 @@
           <t>Cognitive Model</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1538,9 +1550,9 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA5" s="1" t="inlineStr">
-        <is>
-          <t>Dynamic</t>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>Static</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1722,7 +1734,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P6" s="1" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1747,7 +1759,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U6" s="1" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1822,7 +1834,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AK6" s="1" t="inlineStr">
+      <c r="AK6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1954,9 +1966,9 @@
           <t>Dynamic evolution is formalized as ongoing changes in seekers' emotions and chief complaints. Emotion modulation uses an emotion inferencer (trained on D4 dataset with GoEmotions categories) to predict next utterance emotion, plus an emotion perturber with probability-weighted group distances for random perturbation. Chief complaint elicitor generates a complaint change chain before session start and judges whether to switch complaint stage after each round. Tertiary memory divides multi-session memory into real-time memory (current conversation), short-term memory (recent events and self-report scale changes), and long-term memory (previous sessions' conversations and scales), scheduled via Agentic RAG.</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1979,9 +1991,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="R7" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2004,9 +2016,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W7" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -2024,9 +2036,9 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="AA7" s="1" t="inlineStr">
-        <is>
-          <t>Dynamic</t>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>Static</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2034,9 +2046,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AC7" s="1" t="inlineStr">
-        <is>
-          <t>Longitudinal</t>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -2094,9 +2106,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AO7" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -2166,9 +2178,9 @@
           <t>Client Agent</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>Expert Principles/Behavioral Model</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2261,7 +2273,7 @@
           <t>Extended Dialogue</t>
         </is>
       </c>
-      <c r="AD8" s="1" t="inlineStr">
+      <c r="AD8" s="2" t="inlineStr">
         <is>
           <t>Full Disclosure</t>
         </is>
@@ -2276,9 +2288,9 @@
           <t>WAI + BLRI + CCS-R + Big Five + Erikson</t>
         </is>
       </c>
-      <c r="AG8" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -2286,7 +2298,7 @@
           <t>GPT-4o vs human expert consistency score (0.72)</t>
         </is>
       </c>
-      <c r="AI8" s="1" t="inlineStr">
+      <c r="AI8" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2412,9 +2424,9 @@
           <t>When the user sends a message, the LLM is instructed to output a JSON object containing the dynamic fields as well as the final message output. Crucially, these dynamic fields are generated before the output message is generated. This ensures that the generated client message takes into account the newly generated dynamic fields. ... having dynamic fields that are updated by the LLM after each message is sent allows for more adaptive behavior of the client. ... We introduce openness parameter, which is designed to simulate the therapeutic alliance between the client and the trainee. ... openness is determined by the skills the trainee has used in the conversation, which is provided by our skills classification model.</t>
         </is>
       </c>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2427,9 +2439,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P9" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -2462,9 +2474,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W9" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2492,7 +2504,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC9" s="1" t="inlineStr">
+      <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>Extended Dialogue</t>
         </is>
@@ -2627,7 +2639,7 @@
           <t>Therapist Agent</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Surface Persona</t>
         </is>
@@ -2657,9 +2669,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q10" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2762,7 +2774,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AN10" s="1" t="inlineStr">
+      <c r="AN10" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2882,9 +2894,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="R11" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2907,9 +2919,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W11" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2927,9 +2939,9 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr">
-        <is>
-          <t>Static</t>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3172,9 +3184,9 @@
           <t>Longitudinal</t>
         </is>
       </c>
-      <c r="AD12" s="1" t="inlineStr">
-        <is>
-          <t>Full Disclosure</t>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -3312,9 +3324,9 @@
           <t>Dynamic Traits</t>
         </is>
       </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3407,9 +3419,9 @@
           <t>Extended Dialogue</t>
         </is>
       </c>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
-          <t>Full Disclosure</t>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -3972,9 +3984,9 @@
           <t>Human Trainee</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>Expert Principles</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4002,9 +4014,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q16" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -4022,9 +4034,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U16" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -4032,7 +4044,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W16" s="1" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4317,7 +4329,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AI17" s="1" t="inlineStr">
+      <c r="AI17" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4445,7 +4457,7 @@
           <t>Human Trainee</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Surface Persona</t>
         </is>
@@ -4550,9 +4562,9 @@
           <t>NCMHCE (National Clinical Mental Health Counseling Examination) competency framework</t>
         </is>
       </c>
-      <c r="AG18" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -4686,9 +4698,9 @@
           <t>Therapist Agent</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>Expert Principles</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4736,9 +4748,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U19" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -4796,9 +4808,9 @@
           <t>Cognitive Behavioral Therapy (CBT)</t>
         </is>
       </c>
-      <c r="AG19" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -4806,9 +4818,9 @@
           <t>just Level 1：Percentage agreement (agreement rate over 80%)</t>
         </is>
       </c>
-      <c r="AI19" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AI19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -4831,7 +4843,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AN19" s="1" t="inlineStr">
+      <c r="AN19" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4841,9 +4853,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP19" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AP19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4950,9 +4962,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -4990,9 +5002,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V20" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -5170,9 +5182,9 @@
           <t>Therapist Agent</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>Surface Persona</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5205,9 +5217,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="R21" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -5250,9 +5262,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AC21" s="1" t="inlineStr">
-        <is>
-          <t>Short Multi-turn</t>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5280,7 +5292,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AJ21" s="1" t="inlineStr">
+      <c r="AJ21" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5393,9 +5405,9 @@
           <t>Therapist Agent</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>Surface Persona/Dynamic Traits</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Traits</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -5473,7 +5485,7 @@
           <t>Percentage of users who found the chatbot relevant and helpful; Percentage of users who felt comfortable discussing any sensitive topic</t>
         </is>
       </c>
-      <c r="Z22" s="1" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -5488,9 +5500,9 @@
           <t>Short Multi-turn</t>
         </is>
       </c>
-      <c r="AD22" s="1" t="inlineStr">
-        <is>
-          <t>Partial Disclosure</t>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>No Disclosure</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -5626,9 +5638,9 @@
           <t>Therapist Agent</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>Expert Principles/Surface Persona</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -5656,9 +5668,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q23" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -5721,7 +5733,7 @@
           <t>Single-turn</t>
         </is>
       </c>
-      <c r="AD23" s="1" t="inlineStr">
+      <c r="AD23" s="2" t="inlineStr">
         <is>
           <t>Full Disclosure</t>
         </is>
@@ -5786,7 +5798,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AQ23" s="1" t="inlineStr">
+      <c r="AQ23" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5945,9 +5957,9 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA24" s="1" t="inlineStr">
-        <is>
-          <t>Static</t>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -5955,9 +5967,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AC24" s="1" t="inlineStr">
-        <is>
-          <t>Short Multi-turn</t>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5965,7 +5977,7 @@
           <t>Full Disclosure</t>
         </is>
       </c>
-      <c r="AE24" s="1" t="inlineStr">
+      <c r="AE24" s="2" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
@@ -6015,14 +6027,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP24" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AQ24" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AP24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -6030,9 +6042,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AS24" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AS24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6099,14 +6111,14 @@
           <t>Therapist Agent</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Expert Principles</t>
         </is>
       </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -6139,9 +6151,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="R25" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -6169,9 +6181,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X25" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -6179,14 +6191,14 @@
           <t>Accuracy, Precision, Recall, F1 score, PETS (Perceived Empathy of TechNology Scale), LIWC (Linguistic Inquiry and Word Count), Perceived NVC Level, Perceived NVC Effect, Emotional Level (self-assessed), Task Duration, Number of Messages, Kruskal-Wallis tests, Dunn-Bonferroni-Holm post-hoc tests</t>
         </is>
       </c>
-      <c r="Z25" s="1" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="AA25" s="1" t="inlineStr">
-        <is>
-          <t>Static</t>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -6194,9 +6206,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AC25" s="1" t="inlineStr">
-        <is>
-          <t>Short Multi-turn</t>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -6269,7 +6281,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AS25" s="1" t="inlineStr">
+      <c r="AS25" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6347,9 +6359,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -6462,9 +6474,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AK26" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -6487,7 +6499,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP26" s="1" t="inlineStr">
+      <c r="AP26" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6576,9 +6588,9 @@
           <t>Expert Principles</t>
         </is>
       </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -6601,9 +6613,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P27" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -6641,7 +6653,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="X27" s="1" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6656,7 +6668,7 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA27" s="1" t="inlineStr">
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>Dynamic</t>
         </is>
@@ -6686,9 +6698,9 @@
           <t>Hill's Helping Skills framework</t>
         </is>
       </c>
-      <c r="AG27" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -6889,9 +6901,9 @@
           <t>9 Likert-scale questions (1-5) on counseling quality (communication skills, empathy and understanding, professionalism and credibility, therapeutic techniques and skills); identification accuracy (correct/incorrect guesses); Cronbach's alpha (0.92); Mann-Whitney U test; chi-squared test of independence; point-biserial correlation; descriptive statistics (mean, standard deviation)</t>
         </is>
       </c>
-      <c r="Z28" s="1" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -6899,7 +6911,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC28" s="1" t="inlineStr">
+      <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>Short Multi-turn</t>
         </is>
@@ -6909,9 +6921,9 @@
           <t>No Disclosure</t>
         </is>
       </c>
-      <c r="AE28" s="1" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -6929,9 +6941,9 @@
           <t>Cronbach's alpha</t>
         </is>
       </c>
-      <c r="AI28" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -6969,9 +6981,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AQ28" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AQ28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
@@ -7056,9 +7068,9 @@
           <t>Expert Principles</t>
         </is>
       </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -7091,9 +7103,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="R29" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -7121,9 +7133,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="X29" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -7191,9 +7203,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AL29" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AL29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -7399,7 +7411,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AC30" s="1" t="inlineStr">
+      <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>Extended Dialogue</t>
         </is>
@@ -7429,9 +7441,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AJ30" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7459,14 +7471,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP30" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AQ30" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AP30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -7584,9 +7596,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q31" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -7604,9 +7616,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U31" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -7619,9 +7631,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="X31" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -7634,9 +7646,9 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA31" s="1" t="inlineStr">
-        <is>
-          <t>Dynamic</t>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>Static</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -7669,9 +7681,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AI31" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -7704,14 +7716,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP31" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AQ31" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AP31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
@@ -7803,9 +7815,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M32" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -7838,9 +7850,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="T32" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7868,44 +7880,44 @@
           <t>appropriateness, specificity, naturalness, engagement (7-point Likert scale), ranking evaluation via RankME and TrueSkill</t>
         </is>
       </c>
-      <c r="Z32" s="1" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Short Multi-turn</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Short Multi-turn</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>Full Disclosure</t>
-        </is>
-      </c>
-      <c r="AE32" s="1" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
       <c r="AF32" t="inlineStr">
         <is>
           <t>Motivational Interviewing (MI)</t>
         </is>
       </c>
-      <c r="AG32" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -7913,9 +7925,9 @@
           <t>Inter-rater Reliability (Kendall's W)</t>
         </is>
       </c>
-      <c r="AI32" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -7928,7 +7940,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AL32" s="1" t="inlineStr">
+      <c r="AL32" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -7948,9 +7960,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP32" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AP32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -7958,14 +7970,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AR32" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AS32" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AR32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AS32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8041,9 +8053,9 @@
           <t>Client Agent</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>Behavioral State Model/Dynamic Traits</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Behavioral State Model</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -8081,9 +8093,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="R33" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -8126,9 +8138,9 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA33" s="1" t="inlineStr">
-        <is>
-          <t>Static</t>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -8292,9 +8304,9 @@
           <t>Therapist Agent</t>
         </is>
       </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>Dynamic Traits</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Behavioral State Model</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -8352,7 +8364,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V34" s="1" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -8362,9 +8374,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="X34" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -8377,9 +8389,9 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA34" s="1" t="inlineStr">
-        <is>
-          <t>Static</t>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -8452,9 +8464,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP34" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AP34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -8540,9 +8552,9 @@
           <t>Therapist Agent</t>
         </is>
       </c>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>Cognitive Model/Expert Principles</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -8555,9 +8567,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N35" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -8670,9 +8682,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AK35" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -8695,14 +8707,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP35" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AQ35" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AP35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
@@ -8820,9 +8832,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="R36" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -8895,9 +8907,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AJ36" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AJ36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8925,9 +8937,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP36" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AP36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -9051,9 +9063,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="R37" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -9076,9 +9088,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W37" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -9111,9 +9123,9 @@
           <t>Full Disclosure</t>
         </is>
       </c>
-      <c r="AE37" s="1" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -9121,9 +9133,9 @@
           <t>Motivational Interviewing (MI) and Motivational Interviewing Skills Code (MISC)</t>
         </is>
       </c>
-      <c r="AG37" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -9131,9 +9143,9 @@
           <t>ICC / Kendall's Tau</t>
         </is>
       </c>
-      <c r="AI37" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -9303,9 +9315,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S38" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -9328,9 +9340,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="X38" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -9413,9 +9425,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AO38" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
@@ -9423,14 +9435,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AQ38" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AR38" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -9522,14 +9534,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N39" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -9542,9 +9554,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="R39" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -9557,9 +9569,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U39" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -9582,14 +9594,14 @@
           <t>Distinct-1 (D-1), Distinct-2 (D-2), BLEU-1 (B-1), BLEU-2 (B-2), BLEU-3 (B-3), F1, ROUGE-L (R-L), Fluency, Identification, Comforting, Suggestion, Overall</t>
         </is>
       </c>
-      <c r="Z39" s="1" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="AA39" s="1" t="inlineStr">
-        <is>
-          <t>Static</t>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -9607,9 +9619,9 @@
           <t>Full Disclosure</t>
         </is>
       </c>
-      <c r="AE39" s="1" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -9617,9 +9629,9 @@
           <t>Social interdependence theory (Johnson, 2003); Helping Skills Theory (Hill and O'Brien, 1999)</t>
         </is>
       </c>
-      <c r="AG39" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
@@ -9740,14 +9752,14 @@
           <t>SimulationFramework/Dataset</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
-        <is>
-          <t>Therapist Agent</t>
-        </is>
-      </c>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>Cognitive Model / Behavioral State</t>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Client Agent</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Behavioral State Model</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -9780,19 +9792,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R40" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S40" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -9845,7 +9857,7 @@
           <t>Extended Dialogue</t>
         </is>
       </c>
-      <c r="AD40" s="1" t="inlineStr">
+      <c r="AD40" s="2" t="inlineStr">
         <is>
           <t>Full Disclosure</t>
         </is>
@@ -9910,7 +9922,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AR40" s="1" t="inlineStr">
+      <c r="AR40" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -10082,9 +10094,9 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA41" s="1" t="inlineStr">
-        <is>
-          <t>Dynamic</t>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -10337,9 +10349,9 @@
           <t>Extended Dialogue</t>
         </is>
       </c>
-      <c r="AD42" s="1" t="inlineStr">
-        <is>
-          <t>Full Disclosure</t>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
@@ -10352,9 +10364,9 @@
           <t>DSM-V, Beck's cognitive theory, PHQ-9, DBI</t>
         </is>
       </c>
-      <c r="AG42" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -10362,9 +10374,9 @@
           <t>Cohen's Kappa、Correlation Metrics、Win Rate with Expert Calibration</t>
         </is>
       </c>
-      <c r="AI42" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AI42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -10372,12 +10384,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AK42" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AL42" s="1" t="inlineStr">
+      <c r="AK42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL42" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -10397,14 +10409,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP42" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AQ42" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AP42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
@@ -10489,7 +10501,7 @@
           <t>Expert Principles</t>
         </is>
       </c>
-      <c r="K43" s="1" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -10534,9 +10546,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="T43" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -10564,36 +10576,36 @@
           <t>Emotion Mean, Emotion Variability, Average Displacement Length, Emotion Rise Rate, Emotion Recovery Rate, Spearman correlation, Mann–Whitney U test</t>
         </is>
       </c>
-      <c r="Z43" s="1" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>No Disclosure</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Dynamic</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Extended Dialogue</t>
-        </is>
-      </c>
-      <c r="AD43" s="1" t="inlineStr">
-        <is>
-          <t>Full Disclosure</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
       <c r="AF43" t="inlineStr">
         <is>
           <t>Cognitive Behavioral Therapy (CBT)</t>
@@ -10644,9 +10656,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AR43" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AR43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -10721,9 +10733,9 @@
           <t>EvaluationFramework/Benchmark</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr">
-        <is>
-          <t>Human Trainee/Dual-Agent</t>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Persona Agent</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -10756,7 +10768,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q44" s="1" t="inlineStr">
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -10861,9 +10873,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AL44" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AL44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -10891,7 +10903,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AR44" s="1" t="inlineStr">
+      <c r="AR44" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11053,14 +11065,14 @@
           <t>Dialogue Stability (DS), Coherence &amp; Fluency (CF), Emotional Expression (EE), Personalization &amp; Diversity (PD), Accuracy (Acc), Immersion (IM), Coherence (CO), Engagement (EN), Emotional Relief (ER), Satisfaction (SA), Interest (IN), Positive and Negative Affect Schedule (PANAS)</t>
         </is>
       </c>
-      <c r="Z45" s="1" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="AA45" s="1" t="inlineStr">
-        <is>
-          <t>Dynamic</t>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -11073,14 +11085,14 @@
           <t>Extended Dialogue</t>
         </is>
       </c>
-      <c r="AD45" s="1" t="inlineStr">
+      <c r="AD45" s="2" t="inlineStr">
         <is>
           <t>Full Disclosure</t>
         </is>
       </c>
-      <c r="AE45" s="1" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
+          <t>Weak</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -11123,9 +11135,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AO45" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
@@ -11249,9 +11261,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="S46" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -11259,7 +11271,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="U46" s="1" t="inlineStr">
+      <c r="U46" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11284,7 +11296,7 @@
           <t>Emotional Understanding and Empathy (Insight into Patient's Emotional State, Empathetic Response to Emotional Indicators, Consistency and Appropriateness of Empathy, Validation of Patient's Experiences and Emotions, Facilitation of Safe Emotional Expression); Communication and Language (Clarity and Comprehensibility of Communication, Coherence and Relevance in Conversation, Clarity and Conciseness of Information Provided, Handling Misunderstandings, Multilingual Interaction Handling); Engagement and Motivation (Engaging and Motivational Language Usage, Engagement Level in Therapy Sessions, Promotion of Active Participation, Sustaining Patient Interest, Encouragement of AutoNomy and Self-expression, Positive Session Atmosphere); Adaptability and Flexibility (Adaptability to Changing Conversation Dynamics, Response to Novel or Unexpected Inputs, Ability to Redirect Conversation, Flexibility in Conversational Style, Adjustment Based on Feedback, Incorporation of Continuous Improvement Feedback); Therapeutic Effectiveness and Suitability (Overall Effectiveness as a Therapeutic Tool, Meaningful Contributions to Therapy, Suitability for Diverse Patient Groups, Recommendation for Clinical Use, Potential for Future Applications, Compatibility with Various Therapeutic Modalities); Cultural and Sensory Sensitivity (Cultural and Linguistic Sensitivity, Responsiveness to Nonverbal Cues); Stress and Coping Support (Reduction of Patient Stress Levels, Support in Developing Coping Strategies, Enhancement of Communication Skills, Tailored and Personalized Responses); Confidentiality and Privacy (Maintaining Confidentiality and Privacy); Rapport and Trust Building (Building Trust with Patient, Rapport Establishment, Creation of a Safe Environment, Respect for Patient's Boundaries, Consistent Therapeutic Presence)</t>
         </is>
       </c>
-      <c r="Z46" s="1" t="inlineStr">
+      <c r="Z46" s="2" t="inlineStr">
         <is>
           <t>Mentioned</t>
         </is>
@@ -11299,12 +11311,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AC46" s="1" t="inlineStr">
+      <c r="AC46" s="2" t="inlineStr">
         <is>
           <t>Single-turn</t>
         </is>
       </c>
-      <c r="AD46" s="1" t="inlineStr">
+      <c r="AD46" s="2" t="inlineStr">
         <is>
           <t>Partial Disclosure</t>
         </is>
@@ -11329,14 +11341,14 @@
           <t>Delphi consensus method</t>
         </is>
       </c>
-      <c r="AI46" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AJ46" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AI46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -11344,7 +11356,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AL46" s="1" t="inlineStr">
+      <c r="AL46" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -11364,7 +11376,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP46" s="1" t="inlineStr">
+      <c r="AP46" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -11374,14 +11386,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AR46" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AS46" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AR46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AS46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -11498,9 +11510,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U47" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -11593,9 +11605,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP47" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AP47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -11677,9 +11689,9 @@
           <t>CognitiveReframingFramework</t>
         </is>
       </c>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t>Human Trainee/Reframing Assistant</t>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Human Trainee</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -11732,12 +11744,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U48" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V48" s="1" t="inlineStr">
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11747,9 +11759,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="X48" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -11787,9 +11799,9 @@
           <t>CBT (Cognitive Behavioral Therapy) + Cognitive Distortion Theory + Behavioral Activation</t>
         </is>
       </c>
-      <c r="AG48" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -11797,9 +11809,9 @@
           <t>Pearson correlation/p-values with 95% bootstrapped CIs</t>
         </is>
       </c>
-      <c r="AI48" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AI48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -11921,7 +11933,7 @@
           <t>Therapist Agent</t>
         </is>
       </c>
-      <c r="J49" s="1" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Expert Principles</t>
         </is>
@@ -11931,19 +11943,19 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M49" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N49" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O49" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -12001,9 +12013,9 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA49" s="1" t="inlineStr">
-        <is>
-          <t>Dynamic</t>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>Static</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -12011,7 +12023,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AC49" s="1" t="inlineStr">
+      <c r="AC49" s="2" t="inlineStr">
         <is>
           <t>Extended Dialogue</t>
         </is>
@@ -12151,9 +12163,9 @@
           <t>Surface Persona</t>
         </is>
       </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -12231,9 +12243,9 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="AA50" s="1" t="inlineStr">
-        <is>
-          <t>Dynamic</t>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>Static</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -12301,9 +12313,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AP50" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AP50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -12316,9 +12328,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AS50" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AS50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12381,9 +12393,9 @@
           <t>Surface Persona</t>
         </is>
       </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -12411,9 +12423,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q51" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -12456,44 +12468,44 @@
           <t>DiagNostic accuracy, Patient confidence (1-10), Patient compliance (1-10), Patient consultation rating (1-10), Normalized accuracy (Accuracybias/AccuracyNo Bias), Clinician ratings for Doctor realism, Patient realism, Measurement realism, and Empathy (1-10)</t>
         </is>
       </c>
-      <c r="Z51" s="1" t="inlineStr">
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="AE51" s="2" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA51" s="1" t="inlineStr">
-        <is>
-          <t>Dynamic</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Extended Dialogue</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>Full Disclosure</t>
-        </is>
-      </c>
-      <c r="AE51" s="1" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
       <c r="AF51" t="inlineStr">
         <is>
           <t>OSCE + Cognitive Bias + Implicit Bias</t>
         </is>
       </c>
-      <c r="AG51" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -12501,9 +12513,9 @@
           <t>95% CI via bootstrap</t>
         </is>
       </c>
-      <c r="AI51" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AI51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -12531,9 +12543,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AO51" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AO51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
@@ -12606,14 +12618,14 @@
           <t>SimulationFramework, Dataset</t>
         </is>
       </c>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>Dual-Agent</t>
-        </is>
-      </c>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>Cognitive Model/Dynamic Traits</t>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Therapist Agent</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Traits</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -12656,7 +12668,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S52" s="1" t="inlineStr">
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -12671,9 +12683,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V52" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -12766,9 +12778,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AP52" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AP52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -12781,9 +12793,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AS52" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AS52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12905,7 +12917,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U53" s="1" t="inlineStr">
+      <c r="U53" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -12935,7 +12947,7 @@
           <t>Strong</t>
         </is>
       </c>
-      <c r="AA53" s="1" t="inlineStr">
+      <c r="AA53" s="2" t="inlineStr">
         <is>
           <t>Dynamic</t>
         </is>
@@ -12965,7 +12977,7 @@
           <t>Motivational Interviewing (MI)+MISC</t>
         </is>
       </c>
-      <c r="AI53" s="1" t="inlineStr">
+      <c r="AI53" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -12990,7 +13002,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AN53" s="1" t="inlineStr">
+      <c r="AN53" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -13018,6 +13030,5554 @@
       <c r="AS53" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E221"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Paper_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>原值(cxt)</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>修正值</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Eval_Automatic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>人打分后算指标，不是算法自动计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Eval_Lay_Users</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MTurk用户用于生成数据，不是评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>只展示了部分提示词示例，不是全部</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>评估标准为适用性/共情/全面性，未考察角色保真度</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>论文仅做前后测对比(2时间点)，属于STATIC。安全防护代理每3轮分析是干预机制非评估方法 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Uses_Dynamic_State</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>前后测+每3轮持续分析，符合动态状态建模</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Eval_LLM_Judge</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GPT-4o分析每个治疗师话语的治疗动态，属于LLM评估判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>评估的是标注分类准确性，不是角色保真度</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LLM_Judge_Validated</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>有Cohen's Kappa验证标注一致性，得分0.69-0.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>系统有动态设计，但评估只用聚合分数，未分析轮次间变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Eval_Human_Experts</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>专家审查修正主诉链条属数据准备，非评估系统输出。评估环节完全自动化(BERT-score/G-Eval) (校验修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Has_Longitudinal_Eval</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>系统有跨会话设计但评估交互在单会话内完成，不符合纵向评估定义 [人工确认]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Interaction_Level</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Longitudinal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>使用先前会话数据作为上下文，但评估交互本身是在单次扩展对话内完成 [人工确认]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>伦理审查委员会和数据开源限制为伦理声明/措施，非对有害输出的评估 (校验修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>cxt补充仅为系统有用性声明/愿景，非对实用性的评估 (校验修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>明确报告人类专家与GPT-4o平均一致性0.72，属于标准化信度系数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Expert Principles/Behavioral Model</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>证据强调基于专家引导的原则，未提及其他深度模型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>证据表明附录完整披露了多个提示词模板，可复现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>21</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>仅报告平均一致性0.72，未指定统计方法。定义要求kappa/alpha/ICC [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Eval_Human_Experts</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>专家参与标注验证和MI权重编制属数据准备和系统设计，非评估环节 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Eval_LLM_Judge</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MI控制器利用LLM评估MI阶段目标是系统运行时组件，非评估裁判 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Interaction_Level</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>证据表明动态字段每条消息更新，隐含多轮对话，倾向于扩展对话。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>cxt补充仅为系统潜在价值声明，无结构化评估结果 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>29</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Comparable_To_Prior_Work</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>未明确提及与先前研究对比，仅介绍新框架。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>29</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Eval_Automatic</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GPT-4作为裁判进行对比评估属于LLM打分，应归Eval_LLM_Judge。两者互斥 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>29</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>角色指令为表面人设分配。虽在专家数据上微调，无显式专家原则 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>评估了行为时间顺序和适应性，涉及轮次间变化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>31</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>明确说明患者安全不在研究范围内。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>31</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>评估治疗行为质量分类，非实际治疗效果。论文明确声明未纳入患者结局 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>34</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>仅展示示例提示，未披露完整提示词。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>38</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>提示集中展示于图6，但可能不完整。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>38</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Uses_Dynamic_State</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>仅提供静态心理画像，未追踪动态变化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>47</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Eval_Automatic</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>使用LLM-as-Judge(GPT-4o)评估，属Eval_LLM_Judge。LLM打分非算法自动计算 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>47</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>评估侧重安全维度，未评估角色保真度或目标对齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>47</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>仅使用现实世界社交媒体帖子作为输入，未引入专家原则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>47</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>评估了共情、策略等实用维度，直接考察有用性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>49</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>报告三位专家一致评分，明确说明一致同意。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>56</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>仅采用基础提示策略，未构建深度用户画像。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>56</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>仅报告一致数量，未报告标准化信度系数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>58</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>明确报告了一致率超过80%，属于一致性的报告。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>58</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Comparable_To_Prior_Work</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>原始证据未提及与先前研究进行对比，仅是内部专家评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>58</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>评估标准明确要求与CBT案例概念化和取向一致，涉及角色保真度</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>58</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>未涉及不同模型/条件测试或消融实验，仅提出基准</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>58</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>简单角色声明，评估标准存在于评估框架中，非用户画像建模 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>58</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>仅报告百分比一致率，未报告标准化系数如Cohen's kappa或ICC</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>60</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Eval_Lay_Users</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>评估由专家进行，未涉及普通用户</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>60</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Human Learning / Outcomes</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>未评估人类学习或行为改变，仅提及训练局限性</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>63</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Has_Rubric</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>提供了5点李克特量表及明确标签，构成明确评分标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>63</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Interaction_Level</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Short Multi-turn</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>每段对话5-10轮，包含6轮以上情况，符合扩展对话定义</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>63</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>提示词设计旨在贴合治疗师对话风格，体现专家原则</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>63</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>未明确涉及有害输出测试或伦理声明，仅评估适当性</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>65</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Surface Persona/Dynamic Traits</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Dynamic Traits</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>基于大五人格特质建模，属于动态特质</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>65</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>No Disclosure</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>未展示任何提示词内容，不足以复现</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>65</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Theory_Operationalized</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>大五人格理论被用于构建文本分类模型，实现了部分操作化</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>68</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Eval_Automatic</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>仅设计指标，未明确使用算法自动计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>68</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Has_Failure_Analysis</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>原始证据明确提及合成数据偏差导致性能下降，属于失败案例分析。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>68</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Expert Principles/Surface Persona</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>原始证据仅提及‘推进具有同理心、个性化的人工智能解决方案’，未描述具体建模深度，符合表面人设。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>68</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>原始证据指出‘模型还获得了如下明确的指令’，表明prompt已完整披露。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>69</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>原始证据统计了用户消息数量、字符数等分布，属于模式级分析。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>69</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Dataset_Available</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>原始证据仅描述统计结果，未提及数据集公开可用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>69</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Has_Failure_Analysis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>原始证据未涉及失败案例分析。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>69</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>原始证据仅使用单一量表测试假设，未进行多模型/条件鲁棒性测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>69</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Interaction_Level</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Short Multi-turn</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>用户消息中位数10条，属于6轮以上对话。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>69</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Theory_Grounding</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>使用了公认的PETS量表进行测量，理论操作化明确。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>71</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>对LIWC指标取平均值并分析，属于模式级统计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>71</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Dataset_Available</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>补充材料包含FER2013图像名称，源代码公开。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>71</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Emotional Plausibility</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>评估感知共情而非情绪反应的真实性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>71</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Interaction_Level</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Short Multi-turn</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>任务要求5-10分钟对话，同期数据显示用户消息中位数10条/对话，符合扩展对话标准 [人工确认]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>71</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>原始证据明确列出了指导原则如‘跟踪情绪变化’，属于专家原则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>71</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>原始证据未涉及有害输出测试或伦理讨论。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Theory_Operationalized</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>论文仅提及共情的二维结构，未将评估标准明确源自该理论。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Uses_Dynamic_State</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4秒视频缓冲是视觉预处理流水线，非长期心理动态模型的验证 [人工确认]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Eval_Human_Experts</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>论文明确声明未使用真实临床医生互动，未进行领域专家评估。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>在不同LLM和不同障碍类别下测试，进行了鲁棒性测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LLM_Judge_Validated</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>论文仅讨论LLM评估偏差和未来验证需求，未实际验证LLM裁判与人类判断的一致性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>采用配对检验分析干预前后的变化，属于动态分析。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Emotional Plausibility</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>评估了角色真实性，未专门评估情绪反应的真实性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Eval_LLM_Judge</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>使用LLM作为分类器进行技能标注，属于LLM裁判评估。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>虽探索过Cohen's kappa但未报告，因类别不平衡未使用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>75</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Uses_Dynamic_State</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>患者模拟未根据交互调整行为，无动态状态建模。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>仅描述评分方式，未报告评估者间一致性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>77</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Has_Failure_Analysis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>论文未分析失败案例或错误模式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>77</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Interaction_Level</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Short Multi-turn</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Short Multi-turn</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>转录文本时长约5分钟，属于简短多轮对话。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>77</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Theory_Grounding</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>虽提及CBT理论作为基础，但评估问题未明确源于理论。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>77</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Theory_Operationalized</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>论文仅提及CBT理论，但未将评估标准明确操作化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>80</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Emotional Plausibility</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>原始证据未明确提及情绪合理性评估，仅在维度列表中可能包含但未说明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>80</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>原文仅声明无法保证有害输出，并未实际评估安全性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>80</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Uses_Dynamic_State</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>对话历史作为上下文是LLM基本能力，行为原则为静态规则。系统未维护可更新的患者内部状态 [人工确认]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>80</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Uses_Standard_Metrics</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>只是参考先前工作设定了自己的标准，非公认标准指标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>81</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Has_Failure_Analysis</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>未系统性分析失败案例，仅依赖主观感知改进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>81</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>仅声称可应用于其他模型，未实际进行鲁棒性测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>81</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Has_Rubric</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>明确使用了5点李克特量表及标签，提供了评分标准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>81</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Interaction_Level</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>每次会话约10分钟，通常涉及多轮对话，且cxt提供了补充证据倾向此值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>83</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PANAS前后测只对比一次咨询前/后状态，是静态比较，不是轮次间变化分析 (校验修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>83</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>仅提及三位标注员，未报告Cohen's Kappa等标准化一致性指标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>83</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Emotional Plausibility</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>评估标准包括共情能力，但未明确评估情绪反应真实性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>83</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Eval_Automatic</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>G-Eval是LLM打分，PANAS是人工问卷，CTRS是专家打分，都不是算法自动计算 (校验修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>83</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>评估标准为有用性、连贯性等，未涉及角色保真度或目标对齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>83</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Has_Failure_Analysis</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>分析了AI咨询师在CBT技术选择上的局限性，属于失败案例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>83</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>仅设计多样化人格，未进行多模型或对抗测试等鲁棒性检验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>84</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>未报告评估者间一致性系数，仅提及多评估者和平衡设计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>84</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Consistency</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>未考察跨轮次行为稳定性，仅讨论上下文长度的影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>84</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Dataset_Available</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>明确声明数据未公开发布。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>84</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Eval_Human_Experts</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>使用非专家评估，而非领域专家。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>84</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>使用了多个模型（GPT-4、BLOOM、FLAN-T5）和真实对话数据，进行了不同条件测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>84</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>报告了ANOVA和事后检验，但未报告Kappa或ICC等标准化信度系数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>84</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sim_Behavior_Realistic</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>定义了自然性标准并评估了模型输出的真实感，涉及模拟行为真实性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>84</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Theory_Grounding</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>明确基于动机访谈（MI）理论，并引用了经典文献。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>84</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Theory_Operationalized</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>提及理论（咨询研究）但评估标准未完全源于该理论，仅部分操作化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>84</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Uses_Standard_Metrics</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>使用了7点李克特量表这一公认评估指标，并引用了相关文献。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>86</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>评估了动作分布的KL散度，属于统计频率模式，而非动态变化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>86</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Behavioral State Model/Dynamic Traits</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Behavioral State Model</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>建模了动机、信念、偏好、接受性等方面，属于行为状态模型，未明确体现动态特质。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>86</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>未提及有害或偏见输出的评估，仅涉及专家评估MI能力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>87</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>报告了反思问题比、开放式问题比例等行为计数，属于频率模式统计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>87</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Emotional Plausibility</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>评估了共情维度，涉及情绪反应的真实性与恰当性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>87</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>使用了两个不同的大语言模型进行实验，属于不同模型条件下的鲁棒性测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>87</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Human Learning / Outcomes</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>评估的是代理的成功率，而非人类学习或行为改变。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>87</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Dynamic Traits</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Behavioral State Model</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>使用跨理论模型定义了五种离散状态，属于行为状态模型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>89</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Eval_Lay_Users</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>评估团队由心理学专业研究生和治疗师组成，是专家而非普通用户。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>89</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Has_Failure_Analysis</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>仅提到框架局限性，未系统分析具体失败案例或错误模式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>89</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>进行了消融实验，属于不同条件下的鲁棒性测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>89</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>LLM_Judge_Validated</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>使用了两种LLM评估，但未与人类判断进行对比验证。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>89</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Cognitive Model/Expert Principles</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Surface Persona</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>仅用GPT模拟大五人格特质，没有深入认知过程或动态特质。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>91</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>原文明确声明未进行扰动或对抗性输入下的鲁棒性测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>91</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Has_Rubric</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>仅使用F1等指标，未提供明确的评分标准或打分指引。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>91</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>仅涉及分类指标，未评估有害或偏见输出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>92</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>描述了评估过程但未报告评估者间一致性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>92</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>未报告任何标准化信度系数（如Cohen's kappa或ICC）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>92</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>评估了反思在情感和道德上的适当性，涉及安全性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>92</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Theory_Grounding</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>引用了理论但未详细操作化评估标准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>92</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>评估考察了反思是否能提高参与度，即有用性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>93</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Emotional Plausibility</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>原始证据未提及评估情绪反应的真实性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>93</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Has_Failure_Analysis</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>原始证据未涉及失败案例分析。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>93</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Has_Longitudinal_Eval</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>仅提及未来需要纵向研究，当前评估未包含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>93</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Realism</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>未明确评估输出是否像人类。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>93</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sim_Behavior_Realistic</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>未明确评估模拟行为的真实性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>94</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>分析了策略分布，属于模式级别。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>94</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Eval_Lay_Users</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>未提及普通用户参与评估。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>94</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Eval_User_Study</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>标注者静态比较，非真实交互。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>94</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>未明确评估保真度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>94</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>只报告符号检验，未报告kappa或ICC。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>94</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>仅背景说明，未实际测试有害输出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>94</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Theory_Grounding</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>提及理论但未在评估中操作化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>94</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Theory_Operationalized</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>仅提及理论，未操作化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>95</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Eval_Automatic</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>GPT-4O计算技能得分属LLM-as-judge，应归Eval_LLM_Judge。两者互斥 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>95</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Cognitive Model / Behavioral State</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Behavioral State Model</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>证据中抵抗类型分类属于行为状态，认知型仅为子类，未达到认知模型深度</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>95</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>引用官方代码包含完整提示，原则上可复现</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>95</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Realism</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>原始证据未提及真实性评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>95</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>原始证据未涉及安全性评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>95</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Sim_Behavior_Realistic</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>仅描述模型行为，未明确评估模拟行为真实性</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>95</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Simulation_Target</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Therapist Agent</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Client Agent</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>明确使用GPT-3.5作为虚拟客户端</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>97</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>标注话语策略并可视化分布，为统计模式分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>99</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>85.2%准确率为提取验证，非编码者间一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>99</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Has_Failure_Analysis</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>未分析失败案例，仅提及未进行消融实验</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>99</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>未进行多模型/条件鲁棒性测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>99</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>LLM_Judge_Validated</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>未将LLM裁判与人类判断对比</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>99</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>开源数据并提供框架，但未完全披露所有提示词</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>99</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>未报告Cohen's kappa等标准化信度系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>99</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Uses_Standard_Metrics</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>使用5点Likert量表等标准评估指标</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>100</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Consistency</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>未明确评估跨轮次行为一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>100</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>No Disclosure</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>原始证据未披露任何提示词，无法复现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>100</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Sim_Behavior_Realistic</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>论文明确指出合成对话在情绪真实性与真实对话存在差异，表明模拟行为不真实。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>100</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Theory_Operationalized</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>理论仅被用于解释性评论，未明确操作化为评估标准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>100</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Uses_Dynamic_State</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>采用UED框架分析话语序列情绪动态，属于动态状态建模。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>101</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Eval_Automatic</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>PersonaScore是自动计算的指标，符合算法公式自动算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>101</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sim_Behavior_Realistic</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>论文评估的是指标与人类判断的一致性，未直接评估模拟行为真实性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>101</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Simulation_Target</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Human Trainee/Dual-Agent</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Persona Agent</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>论文明确研究角色代理（Persona Agent）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>101</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Uses_Standard_Metrics</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>PersonaScore是作者新提出的指标，非公认标准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>102</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Pattern-level</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>计算平均情绪波动，属于模式层面，未详细分析轮次间变化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>102</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Has_Longitudinal_Eval</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>五轮对话属于单次会话内，非跨会话纵向评估。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>102</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Full Disclosure</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>论文声称附录F包含每个代理的详细提示模板，可复现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>102</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Theory_Grounding</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>引用了理论但未明确操作化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>102</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Theory_Operationalized</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>理论被提及并部分用于定义度量，但操作化不完整。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>104</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>未报告任何评估者间一致性系数（如Kappa/ICC），仅平均分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>104</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Dataset_Available</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>数据可用性声明指出数据包含于文章内，可获取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>104</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>评估的是有效性而非角色保真度</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>104</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>不同提示语属于不同条件测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>104</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Has_Rubric</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>有明确的1-5分量表</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>104</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Interaction_Level</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Single-turn</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Single-turn</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>未明确多轮交互，视为单轮评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>104</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Prompt_Disclosure</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Partial Disclosure</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>披露了初始提示和补充知识，但不足以完全复现</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>104</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Realism</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>评估了清晰性、连贯性等人类语言特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>104</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sim_Behavior_Realistic</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>使用了逼真模拟环境，评估了模拟行为真实性</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>104</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Theory_Operationalized</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>提及德尔菲法和引用文献，但未明确理论操作化</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>104</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Uses_Standard_Metrics</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>使用标准指标并引用文献[48,49]</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>106</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>评估是否遵循CBT结构，符合目标对齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>106</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>与三个基准模型比较属基准对比，非鲁棒性测试 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>107</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>与三个基准模型比较属于标准基准对比，非鲁棒性测试 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>107</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Emotional Plausibility</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>评估共情且基于理论框架，涉及情绪反应</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>107</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>评估的是重构结果质量而非角色保真度</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>107</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Human Learning / Outcomes</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>评估模型输出质量，未考察人类学习效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>107</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>未报告标准化信度系数（如Cohen's kappa或ICC），仅描述评分过程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>107</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Simulation_Target</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Human Trainee/Reframing Assistant</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Human Trainee</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>原始证据显示模型作为重述助手帮助人类重构思维，模拟对象既是人类受训者也是重述助手。</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>108</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>原始证据描述每轮独立评分，未分析行为随轮次变化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>108</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Eval_Human_Experts</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>领域专家仅参与制定标准，未直接参与评分，评估由AMT普通用户完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>108</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Eval_Lay_Users</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>普通用户（AMT标注员）参与评估。</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>108</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Eval_User_Study</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>用户仅对模型输出进行评分，未与系统进行交互实验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>108</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Interaction_Level</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Extended Dialogue</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>对话样本为5-15轮，属于6轮以上扩展对话。</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>108</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Expert Principles</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>模型基于专家定义的支持策略生成回应，体现了专家原则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>109</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>原始证据为空，eval_reports判为Static(85%)。无轮次间变化分析 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>109</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Dataset_Available</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>数据集仅声明将在附录提供，未公开可用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>109</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>仅探索单一模型ChatGPT，未进行多模型或多条件鲁棒性测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>109</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Uses_Dynamic_State</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>提供给LLM的心理画像是静态的一次性注入，交互中无任何状态更新或追踪机制 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>110</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>原始证据仅报告整体准确率，未分析轮次间行为变化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>110</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>仅报告平均评分，未提供标准化信度系数（如Kappa/ICC）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>110</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Eval_Automatic</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>准确率由算法自动计算，属于自动指标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>110</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Has_Longitudinal_Eval</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>交互次数上限变动属单次会话内参数敏感性分析，非跨会话纵向评估 [校验修正]</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>110</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Reliability_Reported</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>报告了三位医生的平均评分，但未报告标准化信度系数如kappa或ICC，仅百分比一致不算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>110</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Theory_Grounding</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>直接引用Blumenthal-Barby &amp; Krieger (2015)定义认知偏差，使用了公认理论。</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>110</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Theory_Operationalized</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Mentioned</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>理论仅被用于解释性评论，未明确操作化为评估标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>110</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Uses_Dynamic_State</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>描述各代理指令和角色，未涉及动态状态建模或随时间更新的状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>111</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Dataset_Available</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>承诺在论文被接收后公开数据，当前未公开，因此不是实际可用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>111</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Has_Robustness_Testing</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>仅在单个数据集上测试模型，未提及其他模型或不同条件测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>111</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Human Learning / Outcomes</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>使用PANAS测量来访者情绪状态变化，显示模型有效减少消极情绪并增强积极情绪</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>111</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Persona_Model_Depth</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Cognitive Model/Dynamic Traits</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Dynamic Traits</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>明确指出动态状态捕捉每次咨询变化，包括不断演变的近期生活经历等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>111</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Realism</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>证据指出模型输出不真实，如给出无关回答，且承认真实性关切，未评估像人类。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>111</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Simulation_Target</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Dual-Agent</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Therapist Agent</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>训练自动心理咨询模型，模拟治疗师角色进行多轮咨询。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>112</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Behavior_Eval_Depth</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>在6个不同时间点评估倾听技能表现，分析行为随轮次的变化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>112</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Coding Options</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>明确报告了机器与人类评分之间的kappa系数范围为0.39至0.79。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>112</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Comparable_To_Prior_Work</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>引用先前研究强调反馈重要性，但本研究未直接与先前结果进行比较。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>112</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>指出模拟患者有时给出无关回答，不符合真实替代角色，考察了保真度。</t>
         </is>
       </c>
     </row>
